--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2513599_ELIMINATORIAS12FINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2513599_ELIMINATORIAS12FINAL_PROCESSED.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.9693</v>
+        <v>9.7484</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4253</v>
+        <v>7.5237</v>
       </c>
       <c r="F2" t="n">
-        <v>2.544</v>
+        <v>2.2248</v>
       </c>
       <c r="G2" t="n">
-        <v>5.313</v>
+        <v>5.3473</v>
       </c>
       <c r="H2" t="n">
-        <v>3.8552</v>
+        <v>3.8734</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4579</v>
+        <v>1.4738</v>
       </c>
       <c r="J2" t="n">
-        <v>4.981</v>
+        <v>5.0811</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3819</v>
+        <v>3.4367</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5991</v>
+        <v>1.6444</v>
       </c>
       <c r="M2" t="n">
-        <v>0.332</v>
+        <v>0.2661</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4733</v>
+        <v>0.4367</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1413</v>
+        <v>-0.1706</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9583</v>
+        <v>-0.2062</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.917</v>
+        <v>0.0621</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0413</v>
+        <v>-0.2683</v>
       </c>
       <c r="V2" t="n">
-        <v>2.3612</v>
+        <v>2.3804</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3612</v>
+        <v>2.3804</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. JANKOVIC</t>
+          <t>S. CECILIA PEREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3957</v>
+        <v>6.2455</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4157</v>
+        <v>5.2117</v>
       </c>
       <c r="F3" t="n">
-        <v>0.98</v>
+        <v>1.0338</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8323</v>
+        <v>0.3691</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4949</v>
+        <v>1.2658</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3374</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9135</v>
+        <v>1.4164</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4119</v>
+        <v>0.829</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5016</v>
+        <v>0.5873</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-1.0472</v>
       </c>
       <c r="N3" t="n">
-        <v>0.083</v>
+        <v>0.4367</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1642</v>
+        <v>-1.484</v>
       </c>
       <c r="P3" t="n">
-        <v>1.4339</v>
+        <v>2.8343</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4582</v>
+        <v>2.8343</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8259</v>
+        <v>-0.7794</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0423</v>
+        <v>-0.0262</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2164</v>
+        <v>-0.7533</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6965</v>
+        <v>3.8215</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4841</v>
+        <v>3.8215</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.1806</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. CECILIA PEREZ</t>
+          <t>M. JANKOVIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.1989</v>
+        <v>4.756</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0991</v>
+        <v>3.9855</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0998</v>
+        <v>0.7705</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3932</v>
+        <v>3.8321</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2792</v>
+        <v>2.5097</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8859</v>
+        <v>1.3224</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3631</v>
+        <v>3.9787</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8058999999999999</v>
+        <v>2.468</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5572</v>
+        <v>1.5107</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9699</v>
+        <v>-0.1467</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4733</v>
+        <v>0.0416</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.4432</v>
+        <v>-0.1883</v>
       </c>
       <c r="P4" t="n">
-        <v>2.8679</v>
+        <v>1.4172</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R4" t="n">
-        <v>2.8679</v>
+        <v>2.4294</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.8461</v>
+        <v>0.1952</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.048</v>
+        <v>0.5172</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7982</v>
+        <v>-0.322</v>
       </c>
       <c r="V4" t="n">
-        <v>3.7839</v>
+        <v>-0.6883</v>
       </c>
       <c r="W4" t="n">
-        <v>3.7839</v>
+        <v>0.5019</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. SOUMBEY-ALLEY</t>
+          <t>A. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.8049</v>
+        <v>4.1597</v>
       </c>
       <c r="E5" t="n">
-        <v>6.4427</v>
+        <v>2.4814</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6377</v>
+        <v>1.6783</v>
       </c>
       <c r="G5" t="n">
-        <v>5.0976</v>
+        <v>2.0497</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4909</v>
+        <v>1.8965</v>
       </c>
       <c r="I5" t="n">
-        <v>4.6067</v>
+        <v>0.1532</v>
       </c>
       <c r="J5" t="n">
-        <v>6.572</v>
+        <v>2.1337</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1044</v>
+        <v>1.8951</v>
       </c>
       <c r="L5" t="n">
-        <v>5.4676</v>
+        <v>0.2385</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4744</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6135</v>
+        <v>0.0013</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8609</v>
+        <v>-0.0853</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4097</v>
+        <v>1.8221</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0485</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6388</v>
+        <v>1.8221</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3591</v>
+        <v>0.4456</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7385</v>
+        <v>0.3477</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3794</v>
+        <v>0.098</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2421</v>
+        <v>-0.1577</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1806</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4227</v>
+        <v>-0.1577</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. LATORRE SANCHEZ</t>
+          <t>L. SOUMBEY-ALLEY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.093</v>
+        <v>4.0948</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2559</v>
+        <v>5.901</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8371</v>
+        <v>-1.8062</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0399</v>
+        <v>5.1421</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8734</v>
+        <v>0.5128</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1664</v>
+        <v>4.6293</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0831</v>
+        <v>6.6541</v>
       </c>
       <c r="K6" t="n">
-        <v>1.846</v>
+        <v>1.1445</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2371</v>
+        <v>5.5097</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0432</v>
+        <v>-1.512</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0275</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0706</v>
+        <v>-0.8804</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8436</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.0245</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8436</v>
+        <v>1.6196</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3453</v>
+        <v>-0.3915</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1728</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1726</v>
+        <v>-0.4727</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1359</v>
+        <v>-0.2509</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.1902</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1359</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="7">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4583</v>
+        <v>2.0968</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7928</v>
+        <v>1.4946</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6654</v>
+        <v>0.6021</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4107</v>
+        <v>-1.424</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8949</v>
+        <v>-0.9086</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5158</v>
+        <v>-0.5154</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.3069</v>
+        <v>-1.2784</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.2569</v>
+        <v>-1.2459</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.05</v>
+        <v>-0.0325</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1038</v>
+        <v>-0.1456</v>
       </c>
       <c r="N7" t="n">
-        <v>0.362</v>
+        <v>0.3373</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4658</v>
+        <v>-0.4829</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4836</v>
+        <v>0.1281</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7385</v>
+        <v>0.3926</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.255</v>
+        <v>-0.2646</v>
       </c>
       <c r="V7" t="n">
-        <v>2.3612</v>
+        <v>2.3804</v>
       </c>
       <c r="W7" t="n">
-        <v>2.3612</v>
+        <v>2.3804</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4943</v>
+        <v>-1.0482</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8844</v>
+        <v>-0.5161</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6099</v>
+        <v>-0.5322</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4532</v>
+        <v>-1.4216</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.8671</v>
+        <v>-1.8397</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4139</v>
+        <v>0.4182</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.4839</v>
+        <v>-1.412</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.9226</v>
+        <v>-1.8801</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4387</v>
+        <v>0.468</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0307</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0555</v>
+        <v>0.0403</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0248</v>
+        <v>-0.0499</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0654</v>
+        <v>-0.6389</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5810999999999999</v>
+        <v>-0.2943</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4842</v>
+        <v>-0.3446</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8711</v>
+        <v>-1.5618</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6346</v>
+        <v>-1.4471</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2366</v>
+        <v>-0.1147</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7157</v>
+        <v>-1.724</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4829</v>
+        <v>-1.4826</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2329</v>
+        <v>-0.2414</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3155</v>
+        <v>-1.3052</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.3155</v>
+        <v>-1.3052</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4003</v>
+        <v>-0.4188</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1674</v>
+        <v>-0.1774</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2329</v>
+        <v>-0.2414</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3602</v>
+        <v>-0.0403</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3191</v>
+        <v>-0.142</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0411</v>
+        <v>0.1017</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. DIBBA</t>
+          <t>N. DEDOVIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1129</v>
+        <v>-2.199</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.082</v>
+        <v>-2.5077</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0309</v>
+        <v>0.3087</v>
       </c>
       <c r="G10" t="n">
-        <v>0.63</v>
+        <v>-1.0881</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6715</v>
+        <v>-0.3946</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0414</v>
+        <v>-0.6935</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3948</v>
+        <v>-1.2254</v>
       </c>
       <c r="K10" t="n">
-        <v>0.644</v>
+        <v>0.0395</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7508</v>
+        <v>-1.2649</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7648</v>
+        <v>0.1373</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0275</v>
+        <v>-0.4341</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7922</v>
+        <v>0.5714</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.8436</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0727</v>
+        <v>-1.0123</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2291</v>
+        <v>0.2025</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0393</v>
+        <v>-0.3011</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3539</v>
+        <v>-0.27</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3146</v>
+        <v>-0.0311</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9385</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2421</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1806</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N. DEDOVIC</t>
+          <t>W. CABRAL BUERIBERI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6699</v>
+        <v>-2.5425</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7758</v>
+        <v>-2.0844</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1059</v>
+        <v>-0.4582</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.074</v>
+        <v>-1.792</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3793</v>
+        <v>-0.4552</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6947</v>
+        <v>-1.3369</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2359</v>
+        <v>-1.0288</v>
       </c>
       <c r="K11" t="n">
-        <v>0.039</v>
+        <v>-0.4162</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.275</v>
+        <v>-0.6126</v>
       </c>
       <c r="M11" t="n">
-        <v>0.162</v>
+        <v>-0.7633</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4183</v>
+        <v>-0.039</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5803</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.8194</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2048</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7765</v>
+        <v>-0.5965</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.2943</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2609</v>
+        <v>-0.3022</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.2509</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2509</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>W. CABRAL BUERIBERI</t>
+          <t>L. DIBBA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8492</v>
+        <v>-2.8669</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3528</v>
+        <v>-1.5033</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4964</v>
+        <v>-1.3636</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.7817</v>
+        <v>0.5813</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4653</v>
+        <v>0.6532</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.3164</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.055</v>
+        <v>1.4073</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4373</v>
+        <v>0.6519</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6177</v>
+        <v>0.7553</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7267</v>
+        <v>-0.826</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.028</v>
+        <v>0.0013</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6987</v>
+        <v>-0.8273</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4097</v>
+        <v>-1.8221</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0242</v>
+        <v>-3.0368</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6145</v>
+        <v>1.2147</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8998</v>
+        <v>-0.6869</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.1248</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3842</v>
+        <v>-0.5621</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2421</v>
+        <v>-0.9393</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>19.9227</v>
+        <v>20.8828</v>
       </c>
       <c r="E13" t="n">
-        <v>16.7019</v>
+        <v>18.5393</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2207</v>
+        <v>2.3433</v>
       </c>
       <c r="G13" t="n">
-        <v>9.870699999999999</v>
+        <v>9.8719</v>
       </c>
       <c r="H13" t="n">
-        <v>5.575599999999999</v>
+        <v>5.630700000000002</v>
       </c>
       <c r="I13" t="n">
-        <v>4.295199999999999</v>
+        <v>4.241099999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>13.9103</v>
+        <v>14.4215</v>
       </c>
       <c r="K13" t="n">
-        <v>5.300800000000001</v>
+        <v>5.617300000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>8.609399999999999</v>
+        <v>8.803900000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.0396</v>
+        <v>-4.549799999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2748999999999999</v>
+        <v>0.01309999999999996</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.314299999999999</v>
+        <v>-4.563</v>
       </c>
       <c r="P13" t="n">
-        <v>7.1695</v>
+        <v>7.086000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-8.193800000000001</v>
+        <v>-8.0982</v>
       </c>
       <c r="R13" t="n">
-        <v>15.3634</v>
+        <v>15.1841</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.8531</v>
+        <v>-2.8719</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8503999999999998</v>
+        <v>0.2492</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.0027</v>
+        <v>-3.1212</v>
       </c>
       <c r="V13" t="n">
-        <v>6.7354</v>
+        <v>6.797</v>
       </c>
       <c r="W13" t="n">
-        <v>11.8358</v>
+        <v>11.9664</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.1004</v>
+        <v>-5.1694</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8227</v>
+        <v>2.8333</v>
       </c>
       <c r="E14" t="n">
-        <v>2.826</v>
+        <v>2.9231</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0032</v>
+        <v>-0.0897</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0003</v>
+        <v>1.0075</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0153</v>
+        <v>2.0162</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.015</v>
+        <v>-1.0087</v>
       </c>
       <c r="J14" t="n">
-        <v>1.857</v>
+        <v>1.9231</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4061</v>
+        <v>2.449</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5492</v>
+        <v>-0.5258</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8567</v>
+        <v>-0.9156</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3909</v>
+        <v>-0.4327</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4658</v>
+        <v>-0.4829</v>
       </c>
       <c r="P14" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S14" t="n">
-        <v>1.085</v>
+        <v>1.097</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4849</v>
+        <v>0.4981</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6001</v>
+        <v>0.5989</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6965</v>
+        <v>-0.6883</v>
       </c>
       <c r="W14" t="n">
-        <v>0.4841</v>
+        <v>0.5019</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="15">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1626</v>
+        <v>0.0871</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.7229</v>
+        <v>-1.2629</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5603</v>
+        <v>1.3499</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0553</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1198</v>
+        <v>-0.1187</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0645</v>
+        <v>0.056</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2402</v>
+        <v>-0.2177</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3982</v>
+        <v>-0.3767</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1581</v>
+        <v>0.159</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1849</v>
+        <v>0.155</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2784</v>
+        <v>0.258</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0935</v>
+        <v>-0.103</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4097</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3024</v>
+        <v>0.5546</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4585</v>
+        <v>-0.033</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7609</v>
+        <v>0.5876</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6353</v>
+        <v>-0.2701</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0354</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6707</v>
+        <v>-1.0942</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4949</v>
+        <v>0.4976</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9483</v>
+        <v>-0.9864000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4432</v>
+        <v>1.484</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6403</v>
+        <v>1.7137</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5016</v>
+        <v>-0.4945</v>
       </c>
       <c r="L16" t="n">
-        <v>2.1419</v>
+        <v>2.2083</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1454</v>
+        <v>-1.2162</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4467</v>
+        <v>-0.4919</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6987</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2925</v>
+        <v>0.6735</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6243</v>
+        <v>0.3251</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3318</v>
+        <v>0.3484</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.7336</v>
+        <v>-1.1276</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3099</v>
+        <v>0.4096</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4238</v>
+        <v>-1.5372</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5571</v>
+        <v>1.5822</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4851</v>
+        <v>-0.4937</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0422</v>
+        <v>2.076</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6044</v>
+        <v>3.7117</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2125</v>
+        <v>0.2548</v>
       </c>
       <c r="L17" t="n">
-        <v>3.3918</v>
+        <v>3.4569</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0473</v>
+        <v>-2.1295</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6976</v>
+        <v>-0.7486</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3496</v>
+        <v>-1.381</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.8921</v>
+        <v>-3.8466</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.3261</v>
+        <v>-5.2637</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6014</v>
+        <v>1.1368</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2313</v>
+        <v>0.7714</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3702</v>
+        <v>0.3654</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. GOMEZ BARRAL</t>
+          <t>G. BLAT BAEZA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.7851</v>
+        <v>-3.3093</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7134</v>
+        <v>-1.8233</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0717</v>
+        <v>-1.486</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.2463</v>
+        <v>-1.1782</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2685</v>
+        <v>-1.6993</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.9779</v>
+        <v>0.5212</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3209</v>
+        <v>0.2758</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5992</v>
+        <v>-1.3848</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7218</v>
+        <v>1.6607</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.9254</v>
+        <v>-1.454</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6693</v>
+        <v>-0.3145</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2561</v>
+        <v>-1.1395</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-1.2147</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2048</v>
+        <v>-2.227</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2048</v>
+        <v>1.0123</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7033</v>
+        <v>0.2738</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8124</v>
+        <v>0.1278</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1091</v>
+        <v>0.146</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2421</v>
+        <v>-1.1902</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2421</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. STOILOV</t>
+          <t>R. GOMEZ BARRAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.6999</v>
+        <v>-3.4283</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0518</v>
+        <v>-1.2049</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.6481</v>
+        <v>-2.2234</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.7875</v>
+        <v>-3.2704</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.4358</v>
+        <v>-1.2841</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3517</v>
+        <v>-1.9863</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8205</v>
+        <v>-1.3017</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.0972</v>
+        <v>-0.5933</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2766</v>
+        <v>-0.7083</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.9669</v>
+        <v>-1.9687</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3386</v>
+        <v>-0.6908</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.6283</v>
+        <v>-1.278</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2048</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.2291</v>
+        <v>-0.2025</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0242</v>
+        <v>0.2025</v>
       </c>
       <c r="S19" t="n">
-        <v>1.7151</v>
+        <v>0.093</v>
       </c>
       <c r="T19" t="n">
-        <v>1.7558</v>
+        <v>0.2992</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0406</v>
+        <v>-0.2062</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.4227</v>
+        <v>-0.2509</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2421</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.6647</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. BLAT BAEZA</t>
+          <t>K. JOHNSON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.8574</v>
+        <v>-4.5664</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2399</v>
+        <v>-0.3961</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6174</v>
+        <v>-4.1702</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1791</v>
+        <v>-0.7693</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6865</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5074</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2169</v>
+        <v>0.4232</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.4072</v>
+        <v>1.0845</v>
       </c>
       <c r="L20" t="n">
-        <v>1.6241</v>
+        <v>-0.6613</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.396</v>
+        <v>-1.1924</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2793</v>
+        <v>-0.9864000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1167</v>
+        <v>-0.206</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.2291</v>
+        <v>-3.2392</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2533</v>
+        <v>-4.049</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0242</v>
+        <v>0.8098</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2685</v>
+        <v>0.0372</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2035</v>
+        <v>0.0033</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.065</v>
+        <v>0.0339</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1806</v>
+        <v>-0.5951</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.2264</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1806</v>
+        <v>-3.8215</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. JOHNSON</t>
+          <t>E. STOILOV</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.8949</v>
+        <v>-4.7205</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7842</v>
+        <v>-0.8865</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.1107</v>
+        <v>-3.834</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.796</v>
+        <v>-3.7923</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0838</v>
+        <v>-2.4128</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8798</v>
+        <v>-1.3795</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3394</v>
+        <v>-0.753</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0321</v>
+        <v>-1.0313</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6927</v>
+        <v>0.2783</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1354</v>
+        <v>-3.0393</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9483</v>
+        <v>-1.3815</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1871</v>
+        <v>-1.6578</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.2776</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.097</v>
+        <v>-1.2147</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8194</v>
+        <v>1.0123</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.231</v>
+        <v>0.7154</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2202</v>
+        <v>0.8302</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0108</v>
+        <v>-0.1149</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5903</v>
+        <v>-1.4411</v>
       </c>
       <c r="W21" t="n">
-        <v>3.1936</v>
+        <v>0.2509</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.7839</v>
+        <v>-1.6921</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9766</v>
+        <v>-4.7285</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2601</v>
+        <v>-0.9265</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.7165</v>
+        <v>-3.802</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.8586</v>
+        <v>-3.8865</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7306</v>
+        <v>-0.7502</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.128</v>
+        <v>-3.1363</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2364</v>
+        <v>-1.2257</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0781</v>
+        <v>0.079</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3145</v>
+        <v>-1.3047</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.6222</v>
+        <v>-2.6608</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8087</v>
+        <v>-0.8292</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.8135</v>
+        <v>-1.8316</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3471</v>
+        <v>-0.0567</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0237</v>
+        <v>0.2992</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3234</v>
+        <v>-0.3559</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-19.9227</v>
+        <v>-19.2303</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2208</v>
+        <v>-2.3434</v>
       </c>
       <c r="F23" t="n">
-        <v>-16.7018</v>
+        <v>-16.8868</v>
       </c>
       <c r="G23" t="n">
-        <v>-9.8705</v>
+        <v>-9.8721</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.575500000000001</v>
+        <v>-5.6309</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.2951</v>
+        <v>-4.241</v>
       </c>
       <c r="J23" t="n">
-        <v>4.04</v>
+        <v>4.5494</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2746</v>
+        <v>-0.01330000000000027</v>
       </c>
       <c r="L23" t="n">
-        <v>4.3143</v>
+        <v>4.5631</v>
       </c>
       <c r="M23" t="n">
-        <v>-13.9104</v>
+        <v>-14.4215</v>
       </c>
       <c r="N23" t="n">
-        <v>-5.301</v>
+        <v>-5.6176</v>
       </c>
       <c r="O23" t="n">
-        <v>-8.609299999999999</v>
+        <v>-8.8041</v>
       </c>
       <c r="P23" t="n">
-        <v>-7.1697</v>
+        <v>-7.0858</v>
       </c>
       <c r="Q23" t="n">
-        <v>-15.3636</v>
+        <v>-15.1839</v>
       </c>
       <c r="R23" t="n">
-        <v>8.193700000000002</v>
+        <v>8.098299999999998</v>
       </c>
       <c r="S23" t="n">
-        <v>3.8531</v>
+        <v>4.5246</v>
       </c>
       <c r="T23" t="n">
-        <v>3.0028</v>
+        <v>3.1213</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8504999999999999</v>
+        <v>1.4032</v>
       </c>
       <c r="V23" t="n">
-        <v>-6.7355</v>
+        <v>-6.7969</v>
       </c>
       <c r="W23" t="n">
-        <v>5.1004</v>
+        <v>5.1694</v>
       </c>
       <c r="X23" t="n">
-        <v>-11.8358</v>
+        <v>-11.9664</v>
       </c>
     </row>
   </sheetData>
